--- a/光伏配储项目/电价数据/2026/浅水站.xlsx
+++ b/光伏配储项目/电价数据/2026/浅水站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50989</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.72027</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56463</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.51581</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44784</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42341</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26784</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21384</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25813</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.0767</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06297999999999999</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05107</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03159</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05276</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03896</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04436</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.00743</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08619</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00195</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00353</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14522</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21297</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23615</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21327</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11456</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00534</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00698</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.15438</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11418</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.19013</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22282</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.17911</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.1119</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12209</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19335</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.26178</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.01151</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.23188</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.01649</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45096</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52678</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.48158</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7609600000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61473</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.50978</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.50661</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.12415</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.58536</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5411</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.26003</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.49916</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50241</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6136</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.56984</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43281</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.46245</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.3909</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62261</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.42793</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75601</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.23635</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9110900000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54548</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52751</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51505</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5109900000000001</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4772</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4253</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52789</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6539400000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7511599999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4426</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.25945</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44686</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08769</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04744</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26238</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.26614</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.21302</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.25532</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.58873</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.20032</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.29144</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.26816</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.5809299999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.02071</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26796</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.22917</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15822</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23194</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.25707</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.24518</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27161</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.26385</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.4678</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.70805</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.9705</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.9028999999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.26509</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8451000000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.42487</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.82197</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43817</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59829</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43381</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33045</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.56043</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47383</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47401</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44289</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40995</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.17693</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.22284</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.25724</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.44547</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.4602</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.20976</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.41913</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21494</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.14618</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20446</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19184</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24749</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27971</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.28547</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.2449</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.21181</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.04243</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28106</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.47655</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.02563</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.49923</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.28545</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34407</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.27193</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27528</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47862</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28205</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26266</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26389</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19354</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10803</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11118</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08112</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.25089</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21279</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.12961</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44752</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21149</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04646</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04732</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06118</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04064</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.01169</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21316</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.00189</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03027</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.04731</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07657</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.20383</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.16737</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20405</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.15269</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19717</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14296</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.20126</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22828</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25705</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.4705299999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25637</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29213</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27699</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04071</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04515</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04025</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04269</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04507</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04558</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04624</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04709000000000001</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04785</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04635</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04668</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04753</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04672999999999999</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.0479</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04641</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04787</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04909</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.0487</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.0464</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04729</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22003</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04647</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04898</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05174</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00214</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14706</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03755</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09884999999999999</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66439</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04262</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04591</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04512</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04402</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04184</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03234</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.0407</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10693</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00105</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03742</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04689</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04112</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04129</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04121</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04376</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.0411</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04052</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0433</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04037</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03899</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0411</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04218</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04266</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04307</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04645000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04604</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20232</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14479</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27137</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33773</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32286</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40735</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28376</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27365</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28337</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17434</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1606</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17323</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14958</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16129</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16068</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23957</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2161</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.2287</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27197</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28853</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28376</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2834100000000001</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27081</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28317</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.23366</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15729</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.27119</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7910900000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9200199999999999</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92789</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.90637</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31919</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.92949</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6387200000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22834</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88922</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.58016</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37316</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06196</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.57324</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.82705</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.80925</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.80629</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8812300000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.89281</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5270199999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43175</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44339</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48861</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25049</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.88005</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55176</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5490700000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5101100000000001</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46111</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42935</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44477</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45325</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42235</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45132</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58966</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59685</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6019800000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6452</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45464</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.53335</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44736</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86497</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5987</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.79367</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.84176</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43419</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.24595</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.40614</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27324</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35329</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02402</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.49916</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.50014</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.61776</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.69197</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.44895</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.50971</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.44709</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50064</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28911</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16473</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28499</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26108</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27591</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.24991</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27496</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42831</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24671</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44704</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5976699999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88976</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.3573</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13669</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71166</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80565</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65132</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5908099999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45102</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50043</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5009100000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39633</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43443</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.45864</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.09208</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.50141</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.008150000000000001</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.63158</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23745</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.5531200000000001</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26224</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.23729</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29141</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26848</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.43062</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.60699</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46569</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.68555</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.4667</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43958</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32651</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2322</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.24204</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23716</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14646</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14914</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15609</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14479</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14483</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14373</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25891</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14545</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26862</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26876</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14331</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05244</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11478</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11372</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14752</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14251</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14776</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40363</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43792</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44179</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44123</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44618</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44545</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40425</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35068</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5346799999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47033</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42541</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.22044</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.21497</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.25767</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.18588</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18215</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.16707</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.2231</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2224</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.17492</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.19509</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.27453</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.25354</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.20791</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.2721</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.28207</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.22709</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.26646</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.25501</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.17498</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.22291</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.22118</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.21289</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44504</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45768</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24915</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.50956</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36064</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28424</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.28839</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.27272</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26942</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03365</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25402</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24998</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.20911</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07468000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18383</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24487</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28621</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25272</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27401</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50417</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.77515</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46661</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.43276</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41688</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30981</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.23982</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.24948</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34721</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.23978</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.73114</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41523</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42957</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64958</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.87552</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.4869</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.48391</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46039</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34507</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26141</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13614</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19526</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.2463</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27856</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.02573</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13029</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.01728</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23739</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24772</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.02463</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23324</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23621</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.61987</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59313</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5591</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46226</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.5893400000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.4777</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.7069</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45358</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45986</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48165</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43059</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49332</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47368</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46615</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4571</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42149</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41401</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41149</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45081</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56132</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50093</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45097</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4196</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42727</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.24874</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2451</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04002</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03199</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.62279</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.26512</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.11251</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.10618</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.00593</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26852</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.03433</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48599</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50842</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.42739</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.56649</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.63947</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.6233500000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.58788</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.64447</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.48762</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.48175</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.70397</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.65524</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44869</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.44158</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.49056</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40843</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.42402</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.43573</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41929</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41158</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.43826</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.43788</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27826</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15811</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27197</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03725</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40858</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45309</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40957</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46406</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01545</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18513</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.39467</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36279</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44377</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.52612</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.55098</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24778</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23539</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23709</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24576</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2518</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03778</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.11955</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.22721</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05439</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17523</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2593</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.03765</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14845</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15244</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.05742</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.00714</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.20147</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.19906</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.13568</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.18073</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2506</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.22228</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.25514</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.25389</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35293</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19411</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.18697</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13202</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.15123</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04464</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01613</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00153</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04362</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04151</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.01607</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.02106</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.14016</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27683</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22409</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22476</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22559</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.22986</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.24029</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26699</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24989</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24334</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23446</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.25056</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25422</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23715</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25534</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24391</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.26126</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24926</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26282</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.27682</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.25961</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21949</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.23947</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21764</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18785</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.08845</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.03446</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.24566</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.04129</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.15959</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15852</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15882</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.02855</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23502</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21862</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.20305</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16742</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15935</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13469</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15931</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.18996</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.11187</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12659</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.19235</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.16256</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.21194</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.18512</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.17262</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.22335</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.17272</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.22333</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.2301</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.21181</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2184</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.13316</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.03915</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.44742</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.20379</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.1729</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16879</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.01381</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04222</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02089</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18783</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.2673</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.03793</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.04357</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.01574</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23431</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25203</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.19253</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32623</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10575</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.26713</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.42492</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25607</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25216</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.11714</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24182</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.09894</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25608</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26981</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.18822</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14354</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10391</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37265</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3321</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.24174</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26487</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27398</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.45362</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.18244</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46162</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25301</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27284</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28319</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26639</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.17006</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26083</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26578</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26269</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.2466</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.22655</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.24335</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.44833</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.42285</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.46644</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.5198400000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.01337</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.44178</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.48363</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.54369</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47532</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45322</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43102</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.8199099999999999</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.4971</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42759</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.44265</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40291</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36903</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46733</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.20617</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17559</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23403</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.28958</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19232</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26396</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.48075</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46545</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.55989</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56389</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46184</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.55159</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49694</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5325700000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52037</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.6858</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7316900000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54975</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5523899999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37681</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27249</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29151</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27255</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26941</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.26828</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.2565</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24966</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.23927</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.2379</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25499</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.19091</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.21313</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13203</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.00821</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.04811</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.09456000000000001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01186</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.12361</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.02225</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.03587</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.0139</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02315</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.02806</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23525</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01731</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03134</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06302000000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11937</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13654</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16417</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22359</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18143</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.18384</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20829</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41826</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38062</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.72897</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27714</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27184</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26129</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23316</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22674</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19581</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19582</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.20019</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21674</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.05842</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.00297</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.0005200000000000001</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-4e-05</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03617</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07919</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.01589</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00431</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01366</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04441</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01028</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01011</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01695</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15569</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.1151</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.02117</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.10578</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.10367</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.08462</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.11074</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.08037000000000001</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.16157</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.13788</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18406</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.23716</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.2677</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.52789</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4084100000000001</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43148</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3821</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.51228</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41735</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23293</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18811</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17307</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11337</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14925</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17583</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.16342</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08813</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10529</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04728</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.07083</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03682</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03742</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03613</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04546</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05206</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06002</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03502</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05699</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07232999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11542</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.14442</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08698</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16475</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14602</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08993000000000001</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04622</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21528</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09662000000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.1879</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.1311</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.1412</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16798</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14725</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.18203</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.20111</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.20213</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21495</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25557</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25952</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26109</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27389</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41315</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4973399999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41815</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44273</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41507</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41449</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38226</v>
       </c>
     </row>
   </sheetData>
